--- a/Base_Dashboard_INDUREC_GAA.xlsx
+++ b/Base_Dashboard_INDUREC_GAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taehy\Downloads\indurec-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526B2EEE-BE75-468C-9D0B-CF124001D812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F40363E-38FC-42C5-A2EF-B49A5F228E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <t>Kanban</t>
   </si>
   <si>
-    <t>Uso correcto de materiales</t>
-  </si>
-  <si>
     <t>Escenario</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
   </si>
   <si>
     <t>Recuperación (meses)</t>
+  </si>
+  <si>
+    <t>Indice de rechazo de materiales</t>
   </si>
 </sst>
 </file>
@@ -626,10 +626,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -742,7 +742,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>3</v>
@@ -759,7 +759,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>4</v>
@@ -776,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>5</v>
@@ -895,7 +895,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>3</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>4</v>
@@ -927,7 +927,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>5</v>
@@ -995,7 +995,7 @@
         <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>3</v>
@@ -1012,7 +1012,7 @@
         <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>4</v>
@@ -1029,7 +1029,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -1065,22 +1065,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
